--- a/Data/Ancot/Milira Race - 3256974620/1.6/Milira Race - 3256974620.xlsx
+++ b/Data/Ancot/Milira Race - 3256974620/1.6/Milira Race - 3256974620.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\optol\OneDrive\바탕 화면\rimpy\translate\임시\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\optol\OneDrive\바탕 화면\rimpy\translate\git\RMK\Data\Ancot\Milira Race - 3256974620\1.6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635BE183-9BB8-45BB-A563-4605428D371C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC36E284-BAF4-4B16-B5FA-6F44CFD80847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="1515" windowWidth="32310" windowHeight="19455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5130" yWindow="4995" windowWidth="31035" windowHeight="19455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11772" uniqueCount="8091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11772" uniqueCount="8093">
   <si>
     <t>Class+Node [(Identifier (Key)]</t>
   </si>
@@ -27431,6 +27431,14 @@
   <si>
     <t>태양단강의 파편입니다. 현재 상태로는 무용지물이지만, 태양 용광로에서 용해하면 일부 자원을 회수할 수 있습니다.</t>
   </si>
+  <si>
+    <t>중형 플로트 유닛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경형 플로트 유닛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -43107,7 +43115,7 @@
         <v>2439</v>
       </c>
       <c r="F900" s="3" t="s">
-        <v>6727</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.3">
@@ -43141,7 +43149,7 @@
         <v>2445</v>
       </c>
       <c r="F902" s="3" t="s">
-        <v>6727</v>
+        <v>8091</v>
       </c>
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.3">
